--- a/data/trending_integrated_20261013_15.xlsx
+++ b/data/trending_integrated_20261013_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F2" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87769564390</v>
+        <v>87787299990</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>전남광주 경제자유구역 확대 추진으로 인한 수혜 기대감. 10년간 움직이지 않던 저항선을 돌파하며 상승 추세 지속 전망.</t>
+          <t>경제자유구역 확대 추진 수혜 기대감 및 10년 저항선 돌파로 인한 상승세 지속 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['대장주', '경제자유구역', '상승 추세']</t>
+          <t>['대장주', '상승세', '경제자유구역']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4605</v>
+        <v>4550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.23%</t>
+          <t>'+16.82%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H3" t="n">
         <v>2.05</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>133013423309</v>
+        <v>137990578304</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>흑사병 테마 관련 치료제 기대감 속 수급 쏠림 및 차익 실현 움직임.</t>
+          <t>러시아 흑사병 테마 관련 국제약품 부각. 뉴스 기반 급등 기대감 존재하나, 개인 물량 털기 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병 테마', '치료제', '수급']</t>
+          <t>['흑사병', '치료제', '뉴스']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>롯데손해보험</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2500</v>
+        <v>17400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.30%</t>
+          <t>'+6.42%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="n">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="G4" t="n">
-        <v>408</v>
+        <v>212</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2330</v>
+        <v>16350</v>
       </c>
       <c r="K4" t="n">
-        <v>2400</v>
+        <v>15790</v>
       </c>
       <c r="L4" t="n">
-        <v>2690</v>
+        <v>19930</v>
       </c>
       <c r="M4" t="n">
-        <v>2110</v>
+        <v>15520</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="O4" t="n">
-        <v>35168552968</v>
+        <v>255533655005</v>
       </c>
       <c r="P4" t="n">
-        <v>3280</v>
+        <v>19930</v>
       </c>
       <c r="Q4" t="n">
-        <v>1576</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-47000</v>
+        <v>42000</v>
       </c>
       <c r="S4" t="n">
-        <v>41000</v>
+        <v>-1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신한금융의 100% 지분 인수 확정 및 시너지 효과 기대감에 따른 급등 전망.</t>
+          <t>보안주 테마 상승 및 신고가 경신 기대감, 단기 과열 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수 확정', '신한금융', '시너지']</t>
+          <t>['보안주', '신고가', '단기과열']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000400</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>롯데손해보험</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11730</v>
+        <v>2470</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.96%</t>
+          <t>'+6.01%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>289</v>
+        <v>131</v>
       </c>
       <c r="F5" t="n">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>570</v>
+        <v>430</v>
       </c>
       <c r="H5" t="n">
-        <v>15.64</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11070</v>
+        <v>2330</v>
       </c>
       <c r="K5" t="n">
-        <v>11670</v>
+        <v>2400</v>
       </c>
       <c r="L5" t="n">
-        <v>13970</v>
+        <v>2690</v>
       </c>
       <c r="M5" t="n">
-        <v>10810</v>
+        <v>2110</v>
       </c>
       <c r="N5" t="n">
-        <v>14.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>396619727570</v>
+        <v>36393392343</v>
       </c>
       <c r="P5" t="n">
-        <v>14350</v>
+        <v>3280</v>
       </c>
       <c r="Q5" t="n">
-        <v>465</v>
+        <v>1576</v>
       </c>
       <c r="R5" t="n">
-        <v>-219000</v>
+        <v>-47000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>테마 영향으로 인한 단기 변동성 확대 및 차익 실현 매물 출회.</t>
+          <t>신한금융의 100% 지분 인수 확정. 목표가 만원 제시 및 시너지 극대화 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['테마주', '단기변동성', '차익실현']</t>
+          <t>['신한금융', '인수', '호재']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>000400</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17220</v>
+        <v>3787</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.32%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.25</v>
+        <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="H6" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16350</v>
+        <v>3710</v>
       </c>
       <c r="K6" t="n">
-        <v>15790</v>
+        <v>3555</v>
       </c>
       <c r="L6" t="n">
-        <v>19930</v>
+        <v>4440</v>
       </c>
       <c r="M6" t="n">
-        <v>15520</v>
+        <v>3475</v>
       </c>
       <c r="N6" t="n">
-        <v>1.13</v>
+        <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>253445684035</v>
+        <v>103737697357</v>
       </c>
       <c r="P6" t="n">
-        <v>19930</v>
+        <v>6660</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>2200</v>
       </c>
       <c r="R6" t="n">
-        <v>42000</v>
+        <v>-70000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>-18000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보안주 테마 상승 및 신고가 경신 기대감, 단기 과열 우려.</t>
+          <t>흑사병 테마 관련 언급과 함께 독감, 코로나 백신 관련 내용 혼재. 대세 상승 시작 주장.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', '신고가', '단기과열']</t>
+          <t>['흑사병 테마', '독감', '코로나 백신']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3785</v>
+        <v>11300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>0.92</v>
       </c>
       <c r="E7" t="n">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="G7" t="n">
-        <v>152</v>
+        <v>590</v>
       </c>
       <c r="H7" t="n">
-        <v>0.91</v>
+        <v>15.64</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3710</v>
+        <v>11070</v>
       </c>
       <c r="K7" t="n">
-        <v>3555</v>
+        <v>11670</v>
       </c>
       <c r="L7" t="n">
-        <v>4440</v>
+        <v>13970</v>
       </c>
       <c r="M7" t="n">
-        <v>3475</v>
+        <v>10810</v>
       </c>
       <c r="N7" t="n">
-        <v>0.78</v>
+        <v>14.72</v>
       </c>
       <c r="O7" t="n">
-        <v>103077059727</v>
+        <v>401660428655</v>
       </c>
       <c r="P7" t="n">
-        <v>6660</v>
+        <v>14350</v>
       </c>
       <c r="Q7" t="n">
-        <v>2200</v>
+        <v>465</v>
       </c>
       <c r="R7" t="n">
-        <v>-70000</v>
+        <v>-219000</v>
       </c>
       <c r="S7" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>흑사병 테마 관련 언급과 함께 독감, 코로나 백신 관련 내용 혼재. 대세 상승 시작 주장.</t>
+          <t>일부 테마 죽음 속에서 전고점 돌파 및 상승 추세 전망. 투자자 이탈 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['흑사병 테마', '독감', '코로나 백신']</t>
+          <t>['전고점', '추세', '테마']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18230</v>
+        <v>18340</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.22%</t>
+          <t>'+1.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="H8" t="n">
         <v>27.69</v>
@@ -1153,7 +1153,7 @@
         <v>17430</v>
       </c>
       <c r="L8" t="n">
-        <v>18250</v>
+        <v>18350</v>
       </c>
       <c r="M8" t="n">
         <v>17210</v>
@@ -1162,7 +1162,7 @@
         <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>75194653995</v>
+        <v>77250534240</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 뉴스 및 기술적 반등 기대감.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시. 기술적 반등 및 주주 환원 정책 요구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 전망', '기술적 반등']</t>
+          <t>['FLNG', '매출', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1560</v>
+        <v>43950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.14%</t>
+          <t>'-1.01%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="G9" t="n">
-        <v>258</v>
+        <v>1148</v>
       </c>
       <c r="H9" t="n">
-        <v>0.32</v>
+        <v>13.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1578</v>
+        <v>44400</v>
       </c>
       <c r="K9" t="n">
-        <v>1578</v>
+        <v>43300</v>
       </c>
       <c r="L9" t="n">
-        <v>1776</v>
+        <v>44850</v>
       </c>
       <c r="M9" t="n">
-        <v>1457</v>
+        <v>42250</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>13.33</v>
       </c>
       <c r="O9" t="n">
-        <v>9431029904</v>
+        <v>34596818675</v>
       </c>
       <c r="P9" t="n">
-        <v>2930</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>910</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>116000</v>
+        <v>90000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
+          <t>리보&amp;캄렐 간암 1차 승인 기대감 및 하반기 시장 주도주 가능성 부각.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
+          <t>['간암 1차 승인', '하반기 시장 주도주', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15870</v>
+        <v>15880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.37%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="H10" t="n">
         <v>9.630000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>64509696320</v>
+        <v>65773987970</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>금감원의 사모펀드 점검 및 공매도 관련 언급. 시세 조정 및 매집 가능성 제기.</t>
+          <t>금감원의 사모펀드 긴급 점검 속 시장 불안정. 지수 폭락에도 버티는 모습 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['사모펀드', '공매도', '시세조정']</t>
+          <t>['사모펀드', '점검', '불안정']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43600</v>
+        <v>70000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>-0.11</v>
       </c>
       <c r="E11" t="n">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F11" t="n">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="G11" t="n">
-        <v>1125</v>
+        <v>812</v>
       </c>
       <c r="H11" t="n">
-        <v>13.1</v>
+        <v>22.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>44400</v>
+        <v>71500</v>
       </c>
       <c r="K11" t="n">
-        <v>43300</v>
+        <v>68400</v>
       </c>
       <c r="L11" t="n">
-        <v>44850</v>
+        <v>70700</v>
       </c>
       <c r="M11" t="n">
-        <v>42250</v>
+        <v>67300</v>
       </c>
       <c r="N11" t="n">
-        <v>13.33</v>
+        <v>22.21</v>
       </c>
       <c r="O11" t="n">
-        <v>33968085375</v>
+        <v>190881313850</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>90000</v>
+        <v>-6000</v>
       </c>
       <c r="S11" t="n">
-        <v>17000</v>
+        <v>-37000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>간암 1차 치료제 승인 기대감 및 공매도 세력과의 공방 예상. AI 분석 기반 긍정 전망.</t>
+          <t>정치권의 주식 시장 개입 및 정책 실패로 인한 투자자 손실 우려. 원전 관련주로서의 기대감과 더불어 반대매매 및 신용 물량 부담.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['간암 치료제', '공매도', 'AI 분석']</t>
+          <t>['원전', '반대매매', '신용 물량']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,182 +1476,182 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69700</v>
+        <v>1543</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.52%</t>
+          <t>'-2.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>262</v>
+        <v>95</v>
       </c>
       <c r="F12" t="n">
-        <v>163</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
-        <v>804</v>
+        <v>258</v>
       </c>
       <c r="H12" t="n">
-        <v>22.1</v>
+        <v>0.32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>71500</v>
+        <v>1578</v>
       </c>
       <c r="K12" t="n">
-        <v>68400</v>
+        <v>1578</v>
       </c>
       <c r="L12" t="n">
-        <v>70700</v>
+        <v>1776</v>
       </c>
       <c r="M12" t="n">
-        <v>67300</v>
+        <v>1457</v>
       </c>
       <c r="N12" t="n">
-        <v>22.21</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>184835066850</v>
+        <v>9509737864</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>2930</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>910</v>
       </c>
       <c r="R12" t="n">
-        <v>-6000</v>
+        <v>116000</v>
       </c>
       <c r="S12" t="n">
-        <v>-37000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치권의 주식 시장 개입 및 정책 실패로 인한 투자자 손실 우려. 원전 관련주로서의 기대감과 더불어 반대매매 및 신용 물량 부담.</t>
+          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '반대매매', '신용 물량']</t>
+          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6560</v>
+        <v>6620</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-3.07%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.3</v>
+        <v>-0.19</v>
       </c>
       <c r="E13" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F13" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>686</v>
+        <v>411</v>
       </c>
       <c r="H13" t="n">
-        <v>12.27</v>
+        <v>1.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6810</v>
+        <v>6830</v>
       </c>
       <c r="K13" t="n">
-        <v>7150</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7160</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>6440</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>12.57</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>22152993935</v>
+        <v>71864000000</v>
       </c>
       <c r="P13" t="n">
-        <v>8850</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4220</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-464000</v>
+        <v>-277000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-218000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 관련 이슈 속 부지 매각 기대감 및 단기 변동성.</t>
+          <t>건설기초소재 대장주로 언급되며 수도권 거점 공장 및 점유율 관련 내용이 있으나, 차트 분석과 더불어 매도 완료 및 밑에서 다시 보자는 의견이 일부 있음. 주포에 대한 부정적인 언급도 존재함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '부지 매각', '단기 변동성']</t>
+          <t>['건설기초소재', '수도권 공장', '주포']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7470</v>
+        <v>7480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.74%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="H14" t="n">
         <v>26.01</v>
@@ -1714,7 +1714,7 @@
         <v>26.37</v>
       </c>
       <c r="O14" t="n">
-        <v>27984407265</v>
+        <v>28556634735</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>회사 경영 관련 부정적 전망 및 주가 하락세 지속.</t>
+          <t>아이폰 패널 출하량 감소 및 부채 상환 목적 유상증자 예상. 지속적 저점 갱신 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['경영 악화', '주가 하락', '유상증자']</t>
+          <t>['아이폰', '패널', '유상증자']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,79 +1759,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5970</v>
+        <v>6560</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.86%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="E15" t="n">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="G15" t="n">
-        <v>146</v>
+        <v>681</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6899999999999999</v>
+        <v>12.27</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6210</v>
+        <v>6810</v>
       </c>
       <c r="K15" t="n">
-        <v>5950</v>
+        <v>7150</v>
       </c>
       <c r="L15" t="n">
-        <v>6560</v>
+        <v>7160</v>
       </c>
       <c r="M15" t="n">
-        <v>5840</v>
+        <v>6440</v>
       </c>
       <c r="N15" t="n">
-        <v>0.75</v>
+        <v>12.57</v>
       </c>
       <c r="O15" t="n">
-        <v>24140565175</v>
+        <v>22477107755</v>
       </c>
       <c r="P15" t="n">
-        <v>11370</v>
+        <v>8850</v>
       </c>
       <c r="Q15" t="n">
-        <v>3300</v>
+        <v>4220</v>
       </c>
       <c r="R15" t="n">
-        <v>75000</v>
+        <v>-464000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>금호타이어 부지 매각 및 영업익, 순익 호조. 공매도 누르기 속 7천원 회복 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['영업익', '순익', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,43 +1839,43 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17780</v>
+        <v>5960</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.15%</t>
+          <t>'-4.03%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.42</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="H16" t="n">
-        <v>0.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18550</v>
+        <v>6210</v>
       </c>
       <c r="K16" t="n">
-        <v>17550</v>
+        <v>5950</v>
       </c>
       <c r="L16" t="n">
-        <v>19580</v>
+        <v>6560</v>
       </c>
       <c r="M16" t="n">
-        <v>17010</v>
+        <v>5840</v>
       </c>
       <c r="N16" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="O16" t="n">
-        <v>76702105245</v>
+        <v>24331572935</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>11370</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>3300</v>
       </c>
       <c r="R16" t="n">
-        <v>-51000</v>
+        <v>75000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12500</v>
+        <v>17640</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.79%</t>
+          <t>'-4.91%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.09</v>
+        <v>-0.42</v>
       </c>
       <c r="E17" t="n">
-        <v>220</v>
+        <v>105</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>342</v>
+        <v>123</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,130 +1975,130 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13410</v>
+        <v>18550</v>
       </c>
       <c r="K17" t="n">
-        <v>13260</v>
+        <v>17550</v>
       </c>
       <c r="L17" t="n">
-        <v>14580</v>
+        <v>19580</v>
       </c>
       <c r="M17" t="n">
-        <v>12430</v>
+        <v>17010</v>
       </c>
       <c r="N17" t="n">
-        <v>0.21</v>
+        <v>0.88</v>
       </c>
       <c r="O17" t="n">
-        <v>69694735475</v>
+        <v>77081023535</v>
       </c>
       <c r="P17" t="n">
-        <v>28700</v>
+        <v>30550</v>
       </c>
       <c r="Q17" t="n">
-        <v>11600</v>
+        <v>6100</v>
       </c>
       <c r="R17" t="n">
-        <v>31000</v>
+        <v>-51000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>명확한 상승 근거 없이 주가 변동성만 커지는 상황. 대차 상환 및 공매도 물량 고려 시 추가 하락 가능성 존재.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주포', '공매도', '변동성']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>172900</v>
+        <v>12480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.44%</t>
+          <t>'-6.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>223</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="G18" t="n">
-        <v>185</v>
+        <v>368</v>
       </c>
       <c r="H18" t="n">
-        <v>75.20999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>186800</v>
+        <v>13410</v>
       </c>
       <c r="K18" t="n">
-        <v>180800</v>
+        <v>13260</v>
       </c>
       <c r="L18" t="n">
-        <v>183000</v>
+        <v>14580</v>
       </c>
       <c r="M18" t="n">
-        <v>170000</v>
+        <v>12400</v>
       </c>
       <c r="N18" t="n">
-        <v>75.23</v>
+        <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>758107296550</v>
+        <v>70189501945</v>
       </c>
       <c r="P18" t="n">
-        <v>243500</v>
+        <v>28700</v>
       </c>
       <c r="Q18" t="n">
-        <v>70400</v>
+        <v>11600</v>
       </c>
       <c r="R18" t="n">
-        <v>-733000</v>
+        <v>31000</v>
       </c>
       <c r="S18" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>주가 하락세 지속 및 공매도 관련 우려로 인한 추가 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,191 +2107,191 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['공매도', '주가 하락', '고점대비']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14510</v>
+        <v>173200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.70%</t>
+          <t>'-7.28%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>492</v>
+        <v>184</v>
       </c>
       <c r="H19" t="n">
-        <v>3.43</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15720</v>
+        <v>186800</v>
       </c>
       <c r="K19" t="n">
-        <v>14770</v>
+        <v>180800</v>
       </c>
       <c r="L19" t="n">
-        <v>15130</v>
+        <v>183000</v>
       </c>
       <c r="M19" t="n">
-        <v>14160</v>
+        <v>170000</v>
       </c>
       <c r="N19" t="n">
-        <v>3.37</v>
+        <v>75.23</v>
       </c>
       <c r="O19" t="n">
-        <v>88433328680</v>
+        <v>789547568450</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>243500</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>70400</v>
       </c>
       <c r="R19" t="n">
-        <v>71000</v>
+        <v>-733000</v>
       </c>
       <c r="S19" t="n">
-        <v>-9000</v>
+        <v>99000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 기록에도 불구하고 미국 업체 기술력 하락 및 전반적인 시장 분위기 악화로 인한 하락세. 7000원선이 바닥일 가능성 제기.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광케이블', '기술력']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>230500</v>
+        <v>14570</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.98%</t>
+          <t>'-7.32%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>128</v>
       </c>
       <c r="F20" t="n">
-        <v>540</v>
+        <v>81</v>
       </c>
       <c r="G20" t="n">
-        <v>1680</v>
+        <v>499</v>
       </c>
       <c r="H20" t="n">
-        <v>46.3</v>
+        <v>3.43</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>250500</v>
+        <v>15720</v>
       </c>
       <c r="K20" t="n">
-        <v>241500</v>
+        <v>14770</v>
       </c>
       <c r="L20" t="n">
-        <v>244000</v>
+        <v>15130</v>
       </c>
       <c r="M20" t="n">
-        <v>228000</v>
+        <v>14160</v>
       </c>
       <c r="N20" t="n">
-        <v>46.35</v>
+        <v>3.37</v>
       </c>
       <c r="O20" t="n">
-        <v>4871191788750</v>
+        <v>89320315890</v>
       </c>
       <c r="P20" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>-5208000</v>
+        <v>71000</v>
       </c>
       <c r="S20" t="n">
-        <v>223000</v>
+        <v>-9000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 여론 확산 및 주가 급락.</t>
+          <t>3분기 어닝 서프라이즈 기록에도 불구하고 미국 업체 기술력 하락 및 전반적인 시장 분위기 악화로 인한 하락세. 7000원선이 바닥일 가능성 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '주가 급락', '부정적 여론']</t>
+          <t>['어닝 서프라이즈', '광케이블', '기술력']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,77 +2304,77 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18750</v>
+        <v>230750</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.31%</t>
+          <t>'-7.88%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.39</v>
+        <v>-0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>329</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>140</v>
+        <v>542</v>
       </c>
       <c r="G21" t="n">
-        <v>477</v>
+        <v>1721</v>
       </c>
       <c r="H21" t="n">
-        <v>0.73</v>
+        <v>46.3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>20450</v>
+        <v>250500</v>
       </c>
       <c r="K21" t="n">
-        <v>19540</v>
+        <v>241500</v>
       </c>
       <c r="L21" t="n">
-        <v>23100</v>
+        <v>244000</v>
       </c>
       <c r="M21" t="n">
-        <v>17540</v>
+        <v>228000</v>
       </c>
       <c r="N21" t="n">
-        <v>0.34</v>
+        <v>46.35</v>
       </c>
       <c r="O21" t="n">
-        <v>99447382195</v>
+        <v>5018615143250</v>
       </c>
       <c r="P21" t="n">
-        <v>62100</v>
+        <v>374500</v>
       </c>
       <c r="Q21" t="n">
-        <v>17540</v>
+        <v>90200</v>
       </c>
       <c r="R21" t="n">
-        <v>-1000</v>
+        <v>-5208000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>223000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>보호예수 이슈 및 주가 조작 의혹 제기. 외부 조달 판매 중심의 기술력 한계로 인해 투자 위험 높음.</t>
+          <t>정치적 이슈로 인한 주가 하락 우려. 외인 매도세 지속 및 정부 시장 개입 비판.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보호예수', '주가 조작', '기술력']</t>
+          <t>['정치', '개입', '외인']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,90 +2396,90 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12160</v>
+        <v>18800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.25%</t>
+          <t>'-8.07%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.01</v>
+        <v>0.39</v>
       </c>
       <c r="E22" t="n">
-        <v>191</v>
+        <v>328</v>
       </c>
       <c r="F22" t="n">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="G22" t="n">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>13400</v>
+        <v>20450</v>
       </c>
       <c r="K22" t="n">
-        <v>13750</v>
+        <v>19540</v>
       </c>
       <c r="L22" t="n">
-        <v>15390</v>
+        <v>23100</v>
       </c>
       <c r="M22" t="n">
-        <v>11980</v>
+        <v>17540</v>
       </c>
       <c r="N22" t="n">
-        <v>1.01</v>
+        <v>0.34</v>
       </c>
       <c r="O22" t="n">
-        <v>198318343685</v>
+        <v>99906607810</v>
       </c>
       <c r="P22" t="n">
-        <v>19380</v>
+        <v>62100</v>
       </c>
       <c r="Q22" t="n">
-        <v>3200</v>
+        <v>17540</v>
       </c>
       <c r="R22" t="n">
-        <v>-22000</v>
+        <v>-1000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 하락 및 외인 매도세 강화, 공매도 관련 우려.</t>
+          <t>주가 조작 의혹 및 계단식 하락 패턴으로 인한 투자 주의 필요.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가 하락', '외인 매도', '공매도']</t>
+          <t>['주가 조작', '계단식 하락', '보호예수']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1438000</v>
+        <v>12120</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.40%</t>
+          <t>'-9.55%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>-1.01</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>195</v>
       </c>
       <c r="F23" t="n">
-        <v>580</v>
+        <v>109</v>
       </c>
       <c r="G23" t="n">
-        <v>1275</v>
+        <v>474</v>
       </c>
       <c r="H23" t="n">
-        <v>49.41</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,38 +2527,38 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1605000</v>
+        <v>13400</v>
       </c>
       <c r="K23" t="n">
-        <v>1538000</v>
+        <v>13750</v>
       </c>
       <c r="L23" t="n">
-        <v>1554000</v>
+        <v>15390</v>
       </c>
       <c r="M23" t="n">
-        <v>1431000</v>
+        <v>11980</v>
       </c>
       <c r="N23" t="n">
-        <v>49.52</v>
+        <v>1.01</v>
       </c>
       <c r="O23" t="n">
-        <v>6592463724000</v>
+        <v>199540674785</v>
       </c>
       <c r="P23" t="n">
-        <v>2987000</v>
+        <v>19380</v>
       </c>
       <c r="Q23" t="n">
-        <v>403000</v>
+        <v>3200</v>
       </c>
       <c r="R23" t="n">
-        <v>-1301000</v>
+        <v>-22000</v>
       </c>
       <c r="S23" t="n">
-        <v>114000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 투자 관련 불확실성으로 인한 주가 하락.</t>
+          <t>주포의 매매 패턴 관찰 및 외인 매수세 하락 압력. 수주 발표 기대감 속 목표가 15000원 제시.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '투자 불확실성', '주가 하락']</t>
+          <t>['주포', '수주', '목표가']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6620</v>
+        <v>1433000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.66%</t>
+          <t>'-10.72%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="E24" t="n">
-        <v>165</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>71</v>
+        <v>579</v>
       </c>
       <c r="G24" t="n">
-        <v>408</v>
+        <v>1427</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>49.41</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7410</v>
+        <v>1605000</v>
       </c>
       <c r="K24" t="n">
-        <v>7330</v>
+        <v>1538000</v>
       </c>
       <c r="L24" t="n">
-        <v>8040</v>
+        <v>1554000</v>
       </c>
       <c r="M24" t="n">
-        <v>6600</v>
+        <v>1425000</v>
       </c>
       <c r="N24" t="n">
-        <v>1.99</v>
+        <v>49.52</v>
       </c>
       <c r="O24" t="n">
-        <v>71435586075</v>
+        <v>6842310645000</v>
       </c>
       <c r="P24" t="n">
-        <v>23500</v>
+        <v>2987000</v>
       </c>
       <c r="Q24" t="n">
-        <v>2890</v>
+        <v>403000</v>
       </c>
       <c r="R24" t="n">
-        <v>-277000</v>
+        <v>-1301000</v>
       </c>
       <c r="S24" t="n">
-        <v>-218000</v>
+        <v>114000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>건설기초소재 대장주로 언급되며 수도권 거점 공장 및 점유율 관련 내용이 있으나, 차트 분석과 더불어 매도 완료 및 밑에서 다시 보자는 의견이 일부 있음. 주포에 대한 부정적인 언급도 존재함.</t>
+          <t>정치적 이슈 및 외인 매도세로 인한 폭락 지속. 추세 전환 없이 하락 관망.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['건설기초소재', '수도권 공장', '주포']</t>
+          <t>['정치', '외인', '폭락']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>000660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_15.xlsx
+++ b/data/trending_integrated_20261013_15.xlsx
@@ -584,7 +584,7 @@
         <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87787299990</v>
+        <v>87880736750</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>경제자유구역 확대 추진 수혜 기대감 및 10년 저항선 돌파로 인한 상승세 지속 전망.</t>
+          <t>호남 반도체 클러스터 수혜주로 언급되며 연상 랠리 기대. 뉴스 기반 대규모 확대 추진 수혜주.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['대장주', '상승세', '경제자유구역']</t>
+          <t>['호남반도체', '수혜주', '연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4550</v>
+        <v>4470</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.82%</t>
+          <t>'+14.76%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
+        <v>204</v>
+      </c>
+      <c r="F3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G3" t="n">
         <v>196</v>
-      </c>
-      <c r="F3" t="n">
-        <v>84</v>
-      </c>
-      <c r="G3" t="n">
-        <v>194</v>
       </c>
       <c r="H3" t="n">
         <v>2.05</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>137990578304</v>
+        <v>141371354160</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>롯데손해보험</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17400</v>
+        <v>2495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.42%</t>
+          <t>'+7.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="F4" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>212</v>
+        <v>452</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16350</v>
+        <v>2330</v>
       </c>
       <c r="K4" t="n">
-        <v>15790</v>
+        <v>2400</v>
       </c>
       <c r="L4" t="n">
-        <v>19930</v>
+        <v>2690</v>
       </c>
       <c r="M4" t="n">
-        <v>15520</v>
+        <v>2110</v>
       </c>
       <c r="N4" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>255533655005</v>
+        <v>37556068403</v>
       </c>
       <c r="P4" t="n">
-        <v>19930</v>
+        <v>3280</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>1576</v>
       </c>
       <c r="R4" t="n">
-        <v>42000</v>
+        <v>-47000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1000</v>
+        <v>41000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>보안주 테마 상승 및 신고가 경신 기대감, 단기 과열 우려.</t>
+          <t>신한금융의 100% 지분 인수 확정 소식 기반 목표가 만원 제시. 2900원 이상의 확정 수익 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', '신고가', '단기과열']</t>
+          <t>['신한금융인수', '목표가', '시너지']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>000400</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>롯데손해보험</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2470</v>
+        <v>17340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.01%</t>
+          <t>'+6.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>430</v>
+        <v>221</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2330</v>
+        <v>16350</v>
       </c>
       <c r="K5" t="n">
-        <v>2400</v>
+        <v>15790</v>
       </c>
       <c r="L5" t="n">
-        <v>2690</v>
+        <v>19930</v>
       </c>
       <c r="M5" t="n">
-        <v>2110</v>
+        <v>15520</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>36393392343</v>
+        <v>257367027775</v>
       </c>
       <c r="P5" t="n">
-        <v>3280</v>
+        <v>19930</v>
       </c>
       <c r="Q5" t="n">
-        <v>1576</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>-47000</v>
+        <v>42000</v>
       </c>
       <c r="S5" t="n">
-        <v>41000</v>
+        <v>-1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신한금융의 100% 지분 인수 확정. 목표가 만원 제시 및 시너지 극대화 기대.</t>
+          <t>미국 보안주 폭락 속에서 10% 이상 상승 기대. 디지털 자산 관련 내용 및 사명 변경 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신한금융', '인수', '호재']</t>
+          <t>['보안주', '디지털자산', '급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000400</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3787</v>
+        <v>3845</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+3.64%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>103737697357</v>
+        <v>104275556981</v>
       </c>
       <c r="P6" t="n">
         <v>6660</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11300</v>
+        <v>11450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+3.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.92</v>
       </c>
       <c r="E7" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G7" t="n">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="H7" t="n">
         <v>15.64</v>
@@ -1070,7 +1070,7 @@
         <v>14.72</v>
       </c>
       <c r="O7" t="n">
-        <v>401660428655</v>
+        <v>404576543495</v>
       </c>
       <c r="P7" t="n">
         <v>14350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>일부 테마 죽음 속에서 전고점 돌파 및 상승 추세 전망. 투자자 이탈 관찰.</t>
+          <t>매도 성공 경험 공유 및 호남 클러스터 외 테마 소멸 전망. 일부 투자자는 내일 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전고점', '추세', '테마']</t>
+          <t>['전고점', '주포', '호남클러스터']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18340</v>
+        <v>18430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.83%</t>
+          <t>'+2.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>446</v>
+        <v>484</v>
       </c>
       <c r="H8" t="n">
         <v>27.69</v>
@@ -1153,7 +1153,7 @@
         <v>17430</v>
       </c>
       <c r="L8" t="n">
-        <v>18350</v>
+        <v>18430</v>
       </c>
       <c r="M8" t="n">
         <v>17210</v>
@@ -1162,7 +1162,7 @@
         <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>77250534240</v>
+        <v>79806565295</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시. 기술적 반등 및 주주 환원 정책 요구.</t>
+          <t>FLNG 매출 3.2조 확대 전망 및 목표가 42,000원 제시. 기술적 반등 및 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FLNG', '매출', '목표가']</t>
+          <t>['FLNG', '목표가', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43950</v>
+        <v>44100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.01%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F9" t="n">
         <v>143</v>
       </c>
       <c r="G9" t="n">
-        <v>1148</v>
+        <v>1169</v>
       </c>
       <c r="H9" t="n">
         <v>13.1</v>
@@ -1254,7 +1254,7 @@
         <v>13.33</v>
       </c>
       <c r="O9" t="n">
-        <v>34596818675</v>
+        <v>35236796925</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>리보&amp;캄렐 간암 1차 승인 기대감 및 하반기 시장 주도주 가능성 부각.</t>
+          <t>FDA 승인 및 NCCN 등재 관련 뉴스 기반 리보세라닙 기대감 상승. 공매도와의 경쟁 지속.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['간암 1차 승인', '하반기 시장 주도주', '공매도']</t>
+          <t>['FDA 승인', '리보세라닙', 'NCCN 등재']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15880</v>
+        <v>15960</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-0.81%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F10" t="n">
         <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="H10" t="n">
         <v>9.630000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>65773987970</v>
+        <v>66970963065</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>금감원의 사모펀드 긴급 점검 속 시장 불안정. 지수 폭락에도 버티는 모습 관찰.</t>
+          <t>전반적인 증시 하락 속에서 주가 하락 경험 공유. 사모펀드 점검 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['사모펀드', '점검', '불안정']</t>
+          <t>['사모펀드', '공매도', '주가하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70000</v>
+        <v>70200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-1.82%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.11</v>
       </c>
       <c r="E11" t="n">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="F11" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G11" t="n">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="H11" t="n">
         <v>22.1</v>
@@ -1438,7 +1438,7 @@
         <v>22.21</v>
       </c>
       <c r="O11" t="n">
-        <v>190881313850</v>
+        <v>195715129850</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.22%</t>
+          <t>'-2.34%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>28</v>
       </c>
       <c r="G12" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H12" t="n">
         <v>0.32</v>
@@ -1530,7 +1530,7 @@
         <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>9509737864</v>
+        <v>9564550742</v>
       </c>
       <c r="P12" t="n">
         <v>2930</v>
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6620</v>
+        <v>7560</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.07%</t>
+          <t>'-2.58%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.19</v>
+        <v>-0.36</v>
       </c>
       <c r="E13" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F13" t="n">
         <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>411</v>
+        <v>472</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8</v>
+        <v>26.01</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6830</v>
+        <v>7760</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>7650</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>7680</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>26.37</v>
       </c>
       <c r="O13" t="n">
-        <v>71864000000</v>
+        <v>29513936235</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="R13" t="n">
-        <v>-277000</v>
+        <v>-908000</v>
       </c>
       <c r="S13" t="n">
-        <v>-218000</v>
+        <v>10000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>건설기초소재 대장주로 언급되며 수도권 거점 공장 및 점유율 관련 내용이 있으나, 차트 분석과 더불어 매도 완료 및 밑에서 다시 보자는 의견이 일부 있음. 주포에 대한 부정적인 언급도 존재함.</t>
+          <t>아이폰 패널 출하량 감소 및 부채 상환 목적 유상증자 예상. 지속적 저점 갱신 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['건설기초소재', '수도권 공장', '주포']</t>
+          <t>['아이폰', '패널', '유상증자']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7480</v>
+        <v>6560</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.36</v>
+        <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F14" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="G14" t="n">
-        <v>469</v>
+        <v>685</v>
       </c>
       <c r="H14" t="n">
-        <v>26.01</v>
+        <v>12.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7760</v>
+        <v>6810</v>
       </c>
       <c r="K14" t="n">
-        <v>7650</v>
+        <v>7150</v>
       </c>
       <c r="L14" t="n">
-        <v>7680</v>
+        <v>7160</v>
       </c>
       <c r="M14" t="n">
-        <v>7300</v>
+        <v>6440</v>
       </c>
       <c r="N14" t="n">
-        <v>26.37</v>
+        <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>28556634735</v>
+        <v>22698120945</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>8850</v>
       </c>
       <c r="Q14" t="n">
-        <v>7300</v>
+        <v>4220</v>
       </c>
       <c r="R14" t="n">
-        <v>-908000</v>
+        <v>-464000</v>
       </c>
       <c r="S14" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>아이폰 패널 출하량 감소 및 부채 상환 목적 유상증자 예상. 지속적 저점 갱신 우려.</t>
+          <t>금호타이어 부지 매각 및 영업익, 순익 호조. 공매도 누르기 속 7천원 회복 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['아이폰', '패널', '유상증자']</t>
+          <t>['영업익', '순익', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>5980</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-3.70%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>72</v>
+      </c>
+      <c r="F15" t="n">
+        <v>28</v>
+      </c>
+      <c r="G15" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>6210</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5950</v>
+      </c>
+      <c r="L15" t="n">
         <v>6560</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>'-3.67%</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>161</v>
-      </c>
-      <c r="F15" t="n">
-        <v>88</v>
-      </c>
-      <c r="G15" t="n">
-        <v>681</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>6810</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7150</v>
-      </c>
-      <c r="L15" t="n">
-        <v>7160</v>
-      </c>
       <c r="M15" t="n">
-        <v>6440</v>
+        <v>5840</v>
       </c>
       <c r="N15" t="n">
-        <v>12.57</v>
+        <v>0.75</v>
       </c>
       <c r="O15" t="n">
-        <v>22477107755</v>
+        <v>24500179095</v>
       </c>
       <c r="P15" t="n">
-        <v>8850</v>
+        <v>11370</v>
       </c>
       <c r="Q15" t="n">
-        <v>4220</v>
+        <v>3300</v>
       </c>
       <c r="R15" t="n">
-        <v>-464000</v>
+        <v>75000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>금호타이어 부지 매각 및 영업익, 순익 호조. 공매도 누르기 속 7천원 회복 기대.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['영업익', '순익', '공매도']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,43 +1839,43 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5960</v>
+        <v>17730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.03%</t>
+          <t>'-4.42%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.06</v>
+        <v>-0.42</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6210</v>
+        <v>18550</v>
       </c>
       <c r="K16" t="n">
-        <v>5950</v>
+        <v>17550</v>
       </c>
       <c r="L16" t="n">
-        <v>6560</v>
+        <v>19580</v>
       </c>
       <c r="M16" t="n">
-        <v>5840</v>
+        <v>17010</v>
       </c>
       <c r="N16" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="O16" t="n">
-        <v>24331572935</v>
+        <v>77361398360</v>
       </c>
       <c r="P16" t="n">
-        <v>11370</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>3300</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>75000</v>
+        <v>-51000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17640</v>
+        <v>14670</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.91%</t>
+          <t>'-6.68%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.42</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="G17" t="n">
-        <v>123</v>
+        <v>515</v>
       </c>
       <c r="H17" t="n">
-        <v>0.46</v>
+        <v>3.43</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,130 +1975,130 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18550</v>
+        <v>15720</v>
       </c>
       <c r="K17" t="n">
-        <v>17550</v>
+        <v>14770</v>
       </c>
       <c r="L17" t="n">
-        <v>19580</v>
+        <v>15130</v>
       </c>
       <c r="M17" t="n">
-        <v>17010</v>
+        <v>14160</v>
       </c>
       <c r="N17" t="n">
-        <v>0.88</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>77081023535</v>
+        <v>90330236990</v>
       </c>
       <c r="P17" t="n">
-        <v>30550</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>6100</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-51000</v>
+        <v>71000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
+          <t>3분기 어닝 서프라이즈 확인, 외인 매수세 유입 가능성. 광케이블 기술력 이슈 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['어닝 서프라이즈', '광케이블', '외인 매수']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12480</v>
+        <v>173800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.94%</t>
+          <t>'-6.96%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>223</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="G18" t="n">
-        <v>368</v>
+        <v>184</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13410</v>
+        <v>186800</v>
       </c>
       <c r="K18" t="n">
-        <v>13260</v>
+        <v>180800</v>
       </c>
       <c r="L18" t="n">
-        <v>14580</v>
+        <v>183000</v>
       </c>
       <c r="M18" t="n">
-        <v>12400</v>
+        <v>170000</v>
       </c>
       <c r="N18" t="n">
-        <v>0.21</v>
+        <v>75.23</v>
       </c>
       <c r="O18" t="n">
-        <v>70189501945</v>
+        <v>814818601350</v>
       </c>
       <c r="P18" t="n">
-        <v>28700</v>
+        <v>243500</v>
       </c>
       <c r="Q18" t="n">
-        <v>11600</v>
+        <v>70400</v>
       </c>
       <c r="R18" t="n">
-        <v>31000</v>
+        <v>-733000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락세 지속 및 공매도 관련 우려로 인한 추가 하락 가능성 제기.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,191 +2107,191 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '고점대비']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>173200</v>
+        <v>12470</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.28%</t>
+          <t>'-7.01%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="G19" t="n">
-        <v>184</v>
+        <v>376</v>
       </c>
       <c r="H19" t="n">
-        <v>75.20999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>186800</v>
+        <v>13410</v>
       </c>
       <c r="K19" t="n">
-        <v>180800</v>
+        <v>13260</v>
       </c>
       <c r="L19" t="n">
-        <v>183000</v>
+        <v>14580</v>
       </c>
       <c r="M19" t="n">
-        <v>170000</v>
+        <v>12390</v>
       </c>
       <c r="N19" t="n">
-        <v>75.23</v>
+        <v>0.21</v>
       </c>
       <c r="O19" t="n">
-        <v>789547568450</v>
+        <v>70788941645</v>
       </c>
       <c r="P19" t="n">
-        <v>243500</v>
+        <v>28700</v>
       </c>
       <c r="Q19" t="n">
-        <v>70400</v>
+        <v>11600</v>
       </c>
       <c r="R19" t="n">
-        <v>-733000</v>
+        <v>31000</v>
       </c>
       <c r="S19" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>고점 대비 60% 하락, 공매도 잔고 높은 상황. 향후 추가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['공매도', '하락', '상폐']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14570</v>
+        <v>232500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.32%</t>
+          <t>'-7.19%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>128</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>81</v>
+        <v>538</v>
       </c>
       <c r="G20" t="n">
-        <v>499</v>
+        <v>1650</v>
       </c>
       <c r="H20" t="n">
-        <v>3.43</v>
+        <v>46.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15720</v>
+        <v>250500</v>
       </c>
       <c r="K20" t="n">
-        <v>14770</v>
+        <v>241500</v>
       </c>
       <c r="L20" t="n">
-        <v>15130</v>
+        <v>244000</v>
       </c>
       <c r="M20" t="n">
-        <v>14160</v>
+        <v>228000</v>
       </c>
       <c r="N20" t="n">
-        <v>3.37</v>
+        <v>46.35</v>
       </c>
       <c r="O20" t="n">
-        <v>89320315890</v>
+        <v>5143648136000</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R20" t="n">
-        <v>71000</v>
+        <v>-5208000</v>
       </c>
       <c r="S20" t="n">
-        <v>-9000</v>
+        <v>223000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 기록에도 불구하고 미국 업체 기술력 하락 및 전반적인 시장 분위기 악화로 인한 하락세. 7000원선이 바닥일 가능성 제기.</t>
+          <t>현 정부 정책에 대한 부정적 평가와 함께 주가 하락 경험 공유. 외인 매도세 및 노조 관련 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광케이블', '기술력']</t>
+          <t>['정부개입', '호남반도체', '외인매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,77 +2304,77 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>230750</v>
+        <v>18890</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.88%</t>
+          <t>'-7.63%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.05</v>
+        <v>0.39</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>330</v>
       </c>
       <c r="F21" t="n">
-        <v>542</v>
+        <v>140</v>
       </c>
       <c r="G21" t="n">
-        <v>1721</v>
+        <v>491</v>
       </c>
       <c r="H21" t="n">
-        <v>46.3</v>
+        <v>0.73</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>250500</v>
+        <v>20450</v>
       </c>
       <c r="K21" t="n">
-        <v>241500</v>
+        <v>19540</v>
       </c>
       <c r="L21" t="n">
-        <v>244000</v>
+        <v>23100</v>
       </c>
       <c r="M21" t="n">
-        <v>228000</v>
+        <v>17540</v>
       </c>
       <c r="N21" t="n">
-        <v>46.35</v>
+        <v>0.34</v>
       </c>
       <c r="O21" t="n">
-        <v>5018615143250</v>
+        <v>100376259070</v>
       </c>
       <c r="P21" t="n">
-        <v>374500</v>
+        <v>62100</v>
       </c>
       <c r="Q21" t="n">
-        <v>90200</v>
+        <v>17540</v>
       </c>
       <c r="R21" t="n">
-        <v>-5208000</v>
+        <v>-1000</v>
       </c>
       <c r="S21" t="n">
-        <v>223000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 주가 하락 우려. 외인 매도세 지속 및 정부 시장 개입 비판.</t>
+          <t>주가 조작 의혹 및 계단식 하락 패턴으로 인한 투자 주의 필요.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['정치', '개입', '외인']</t>
+          <t>['주가 조작', '계단식 하락', '보호예수']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,90 +2396,90 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18800</v>
+        <v>12110</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.07%</t>
+          <t>'-9.63%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.39</v>
+        <v>-1.01</v>
       </c>
       <c r="E22" t="n">
-        <v>328</v>
+        <v>198</v>
       </c>
       <c r="F22" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="G22" t="n">
         <v>483</v>
       </c>
       <c r="H22" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>20450</v>
+        <v>13400</v>
       </c>
       <c r="K22" t="n">
-        <v>19540</v>
+        <v>13750</v>
       </c>
       <c r="L22" t="n">
-        <v>23100</v>
+        <v>15390</v>
       </c>
       <c r="M22" t="n">
-        <v>17540</v>
+        <v>11980</v>
       </c>
       <c r="N22" t="n">
-        <v>0.34</v>
+        <v>1.01</v>
       </c>
       <c r="O22" t="n">
-        <v>99906607810</v>
+        <v>200043579885</v>
       </c>
       <c r="P22" t="n">
-        <v>62100</v>
+        <v>19380</v>
       </c>
       <c r="Q22" t="n">
-        <v>17540</v>
+        <v>3200</v>
       </c>
       <c r="R22" t="n">
-        <v>-1000</v>
+        <v>-22000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 계단식 하락 패턴으로 인한 투자 주의 필요.</t>
+          <t>주포의 움직임과 공매도에 대한 언급. 목표가 15000원 제시 및 호남 반도체 관련 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가 조작', '계단식 하락', '보호예수']</t>
+          <t>['주포', '공매도', '호남반도체']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12120</v>
+        <v>1443000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.55%</t>
+          <t>'-10.09%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E23" t="n">
-        <v>195</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>109</v>
+        <v>579</v>
       </c>
       <c r="G23" t="n">
-        <v>474</v>
+        <v>1484</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>49.41</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,38 +2527,38 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>13400</v>
+        <v>1605000</v>
       </c>
       <c r="K23" t="n">
-        <v>13750</v>
+        <v>1538000</v>
       </c>
       <c r="L23" t="n">
-        <v>15390</v>
+        <v>1554000</v>
       </c>
       <c r="M23" t="n">
-        <v>11980</v>
+        <v>1425000</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>49.52</v>
       </c>
       <c r="O23" t="n">
-        <v>199540674785</v>
+        <v>7032658543000</v>
       </c>
       <c r="P23" t="n">
-        <v>19380</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>3200</v>
+        <v>403000</v>
       </c>
       <c r="R23" t="n">
-        <v>-22000</v>
+        <v>-1301000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>114000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>주포의 매매 패턴 관찰 및 외인 매수세 하락 압력. 수주 발표 기대감 속 목표가 15000원 제시.</t>
+          <t>현 정부 정책 및 이재명 관련 부정적 평가와 함께 주가 폭락 경험 공유. 외인 매도세 및 최태원 관련 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['주포', '수주', '목표가']</t>
+          <t>['이재명', '호남투자', '외인매도']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1433000</v>
+        <v>6640</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.72%</t>
+          <t>'-10.39%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="E24" t="n">
-        <v>800</v>
+        <v>170</v>
       </c>
       <c r="F24" t="n">
-        <v>579</v>
+        <v>72</v>
       </c>
       <c r="G24" t="n">
-        <v>1427</v>
+        <v>421</v>
       </c>
       <c r="H24" t="n">
-        <v>49.41</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1605000</v>
+        <v>7410</v>
       </c>
       <c r="K24" t="n">
-        <v>1538000</v>
+        <v>7330</v>
       </c>
       <c r="L24" t="n">
-        <v>1554000</v>
+        <v>8040</v>
       </c>
       <c r="M24" t="n">
-        <v>1425000</v>
+        <v>6580</v>
       </c>
       <c r="N24" t="n">
-        <v>49.52</v>
+        <v>1.99</v>
       </c>
       <c r="O24" t="n">
-        <v>6842310645000</v>
+        <v>72145361100</v>
       </c>
       <c r="P24" t="n">
-        <v>2987000</v>
+        <v>23500</v>
       </c>
       <c r="Q24" t="n">
-        <v>403000</v>
+        <v>2890</v>
       </c>
       <c r="R24" t="n">
-        <v>-1301000</v>
+        <v>-277000</v>
       </c>
       <c r="S24" t="n">
-        <v>114000</v>
+        <v>-218000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 외인 매도세로 인한 폭락 지속. 추세 전환 없이 하락 관망.</t>
+          <t>성수 메가프로젝트 및 건설 기초소재 관련 언급. 매수 호가 대량 물량 및 매집 물량 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['정치', '외인', '폭락']</t>
+          <t>['건설기초소재', '매집', '호남반도체']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>038500</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_15.xlsx
+++ b/data/trending_integrated_20261013_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F2" t="n">
         <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87880736750</v>
+        <v>87909833670</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 수혜주로 언급되며 연상 랠리 기대. 뉴스 기반 대규모 확대 추진 수혜주.</t>
+          <t>전남광주 경제자유구역 확대 추진 수혜 기대. 10년간 꿈쩍 않던 자리 돌파.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남반도체', '수혜주', '연상']</t>
+          <t>['경제자유구역', '수혜주', '상승']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4470</v>
+        <v>4495</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.76%</t>
+          <t>'+15.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H3" t="n">
         <v>2.05</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>141371354160</v>
+        <v>141841396310</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>러시아 흑사병 테마 관련 국제약품 부각. 뉴스 기반 급등 기대감 존재하나, 개인 물량 털기 관찰.</t>
+          <t>러시아 흑사병 테마 관련 신풍제약 비교 및 기대감 형성. 질병청 발표와 상반된 투자 심리.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병', '치료제', '뉴스']</t>
+          <t>['흑사병', '치료제', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2495</v>
+        <v>2515</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.08%</t>
+          <t>'+7.94%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="H4" t="n">
         <v>0.9399999999999999</v>
@@ -794,7 +794,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>37556068403</v>
+        <v>37845152563</v>
       </c>
       <c r="P4" t="n">
         <v>3280</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신한금융의 100% 지분 인수 확정 소식 기반 목표가 만원 제시. 2900원 이상의 확정 수익 전망.</t>
+          <t>신한금융의 100% 지분 인수 확정 및 시너지 극대화 기대. 최소 2900원 공개매수 가격 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신한금융인수', '목표가', '시너지']</t>
+          <t>['신한금융', '인수', '호재']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F5" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H5" t="n">
         <v>0.88</v>
@@ -886,7 +886,7 @@
         <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>257367027775</v>
+        <v>257807221015</v>
       </c>
       <c r="P5" t="n">
         <v>19930</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3845</v>
+        <v>3895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.64%</t>
+          <t>'+4.99%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>104275556981</v>
+        <v>104555958031</v>
       </c>
       <c r="P6" t="n">
         <v>6660</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11450</v>
+        <v>11500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.43%</t>
+          <t>'+3.88%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.92</v>
       </c>
       <c r="E7" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F7" t="n">
         <v>144</v>
       </c>
       <c r="G7" t="n">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="H7" t="n">
         <v>15.64</v>
@@ -1070,7 +1070,7 @@
         <v>14.72</v>
       </c>
       <c r="O7" t="n">
-        <v>404576543495</v>
+        <v>405253502495</v>
       </c>
       <c r="P7" t="n">
         <v>14350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>매도 성공 경험 공유 및 호남 클러스터 외 테마 소멸 전망. 일부 투자자는 내일 상승 기대.</t>
+          <t>단기 고점 매도 성공 및 재매수 시점 탐색. 호남클러스터 외 테마 소멸 분석.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전고점', '주포', '호남클러스터']</t>
+          <t>['전고점', '매도', '재매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18430</v>
+        <v>18360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.33%</t>
+          <t>'+1.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="H8" t="n">
         <v>27.69</v>
@@ -1162,7 +1162,7 @@
         <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>79806565295</v>
+        <v>85616385335</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FLNG 매출 3.2조 확대 전망 및 목표가 42,000원 제시. 기술적 반등 및 공매도 금지 요구.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 상향. 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FLNG', '목표가', '공매도']</t>
+          <t>['FLNG', '전망', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44100</v>
+        <v>44000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.90%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G9" t="n">
-        <v>1169</v>
+        <v>1192</v>
       </c>
       <c r="H9" t="n">
         <v>13.1</v>
@@ -1254,7 +1254,7 @@
         <v>13.33</v>
       </c>
       <c r="O9" t="n">
-        <v>35236796925</v>
+        <v>35773420925</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 승인 및 NCCN 등재 관련 뉴스 기반 리보세라닙 기대감 상승. 공매도와의 경쟁 지속.</t>
+          <t>HLB, 리보&amp;캄렐 간암 1차 승인 기대감 및 NCCN 등재 뉴스 기반으로 주가 상승 전망. 공매도 세력과의 시각차 및 통합 IR 데이 주목.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '리보세라닙', 'NCCN 등재']</t>
+          <t>['리보세라닙', '캄렐리주맙', 'NCCN 등재']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15960</v>
+        <v>70200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.81%</t>
+          <t>'-1.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="E10" t="n">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="F10" t="n">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="G10" t="n">
-        <v>520</v>
+        <v>818</v>
       </c>
       <c r="H10" t="n">
-        <v>9.630000000000001</v>
+        <v>22.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16090</v>
+        <v>71500</v>
       </c>
       <c r="K10" t="n">
-        <v>15190</v>
+        <v>68400</v>
       </c>
       <c r="L10" t="n">
-        <v>16050</v>
+        <v>70700</v>
       </c>
       <c r="M10" t="n">
-        <v>15100</v>
+        <v>67300</v>
       </c>
       <c r="N10" t="n">
-        <v>9.470000000000001</v>
+        <v>22.21</v>
       </c>
       <c r="O10" t="n">
-        <v>66970963065</v>
+        <v>203893921250</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>658000</v>
+        <v>-6000</v>
       </c>
       <c r="S10" t="n">
-        <v>60000</v>
+        <v>-37000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>전반적인 증시 하락 속에서 주가 하락 경험 공유. 사모펀드 점검 및 공매도 관련 언급.</t>
+          <t>정치권의 주식 시장 개입 및 정책 실패로 인한 투자자 손실 우려. 원전 관련주로서의 기대감과 더불어 반대매매 및 신용 물량 부담.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['사모펀드', '공매도', '주가하락']</t>
+          <t>['원전', '반대매매', '신용 물량']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,283 +1384,283 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70200</v>
+        <v>1544</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.82%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>277</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>815</v>
+        <v>262</v>
       </c>
       <c r="H11" t="n">
-        <v>22.1</v>
+        <v>0.32</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>71500</v>
+        <v>1578</v>
       </c>
       <c r="K11" t="n">
-        <v>68400</v>
+        <v>1578</v>
       </c>
       <c r="L11" t="n">
-        <v>70700</v>
+        <v>1776</v>
       </c>
       <c r="M11" t="n">
-        <v>67300</v>
+        <v>1457</v>
       </c>
       <c r="N11" t="n">
-        <v>22.21</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>195715129850</v>
+        <v>9578528574</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>2930</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>910</v>
       </c>
       <c r="R11" t="n">
-        <v>-6000</v>
+        <v>116000</v>
       </c>
       <c r="S11" t="n">
-        <v>-37000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치권의 주식 시장 개입 및 정책 실패로 인한 투자자 손실 우려. 원전 관련주로서의 기대감과 더불어 반대매매 및 신용 물량 부담.</t>
+          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '반대매매', '신용 물량']</t>
+          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1541</v>
+        <v>7560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.34%</t>
+          <t>'-2.58%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="G12" t="n">
-        <v>259</v>
+        <v>474</v>
       </c>
       <c r="H12" t="n">
-        <v>0.32</v>
+        <v>26.01</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1578</v>
+        <v>7760</v>
       </c>
       <c r="K12" t="n">
-        <v>1578</v>
+        <v>7650</v>
       </c>
       <c r="L12" t="n">
-        <v>1776</v>
+        <v>7680</v>
       </c>
       <c r="M12" t="n">
-        <v>1457</v>
+        <v>7300</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>26.37</v>
       </c>
       <c r="O12" t="n">
-        <v>9564550742</v>
+        <v>31519347195</v>
       </c>
       <c r="P12" t="n">
-        <v>2930</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>910</v>
+        <v>7300</v>
       </c>
       <c r="R12" t="n">
-        <v>116000</v>
+        <v>-908000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
+          <t>아이폰 패널 출하량 감소 및 부채 상환 목적 유상증자 예상. 지속적 저점 갱신 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
+          <t>['아이폰', '패널', '유상증자']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7560</v>
+        <v>6000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.58%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.36</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>472</v>
+        <v>154</v>
       </c>
       <c r="H13" t="n">
-        <v>26.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7760</v>
+        <v>6210</v>
       </c>
       <c r="K13" t="n">
-        <v>7650</v>
+        <v>5950</v>
       </c>
       <c r="L13" t="n">
-        <v>7680</v>
+        <v>6560</v>
       </c>
       <c r="M13" t="n">
-        <v>7300</v>
+        <v>5840</v>
       </c>
       <c r="N13" t="n">
-        <v>26.37</v>
+        <v>0.75</v>
       </c>
       <c r="O13" t="n">
-        <v>29513936235</v>
+        <v>24596281095</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>11370</v>
       </c>
       <c r="Q13" t="n">
-        <v>7300</v>
+        <v>3300</v>
       </c>
       <c r="R13" t="n">
-        <v>-908000</v>
+        <v>75000</v>
       </c>
       <c r="S13" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아이폰 패널 출하량 감소 및 부채 상환 목적 유상증자 예상. 지속적 저점 갱신 우려.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['아이폰', '패널', '유상증자']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H14" t="n">
         <v>12.27</v>
@@ -1714,7 +1714,7 @@
         <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>22698120945</v>
+        <v>22985455505</v>
       </c>
       <c r="P14" t="n">
         <v>8850</v>
@@ -1759,92 +1759,92 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5980</v>
+        <v>15960</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-3.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>0.16</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="G15" t="n">
-        <v>150</v>
+        <v>528</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6210</v>
+        <v>16610</v>
       </c>
       <c r="K15" t="n">
-        <v>5950</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6560</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5840</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>24500179095</v>
+        <v>69591000000</v>
       </c>
       <c r="P15" t="n">
-        <v>11370</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>75000</v>
+        <v>658000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>전반적인 증시 하락 속에서 주가 하락 경험 공유. 사모펀드 점검 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['사모펀드', '공매도', '주가하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17730</v>
+        <v>17740</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.42%</t>
+          <t>'-4.37%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1898,7 +1898,7 @@
         <v>0.88</v>
       </c>
       <c r="O16" t="n">
-        <v>77361398360</v>
+        <v>77570960980</v>
       </c>
       <c r="P16" t="n">
         <v>30550</v>
@@ -1958,13 +1958,13 @@
         <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F17" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G17" t="n">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="H17" t="n">
         <v>3.43</v>
@@ -1990,7 +1990,7 @@
         <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>90330236990</v>
+        <v>91020929930</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 확인, 외인 매수세 유입 가능성. 광케이블 기술력 이슈 존재.</t>
+          <t>3분기 어닝 서프라이즈 기록. 외인 매수세 유입에도 불구하고 주가 부진.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광케이블', '외인 매수']</t>
+          <t>['어닝서프라이즈', '외인매수', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>173800</v>
+        <v>174300</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.96%</t>
+          <t>'-6.69%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F18" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H18" t="n">
         <v>75.20999999999999</v>
@@ -2082,7 +2082,7 @@
         <v>75.23</v>
       </c>
       <c r="O18" t="n">
-        <v>814818601350</v>
+        <v>878915160450</v>
       </c>
       <c r="P18" t="n">
         <v>243500</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12470</v>
+        <v>12490</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.01%</t>
+          <t>'-6.86%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.09</v>
       </c>
       <c r="E19" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F19" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G19" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H19" t="n">
         <v>0.3</v>
@@ -2174,7 +2174,7 @@
         <v>0.21</v>
       </c>
       <c r="O19" t="n">
-        <v>70788941645</v>
+        <v>70888761725</v>
       </c>
       <c r="P19" t="n">
         <v>28700</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>고점 대비 60% 하락, 공매도 잔고 높은 상황. 향후 추가 하락 가능성 언급.</t>
+          <t>고점 대비 큰 폭 하락 및 공매도 잔고 누적. 투자자들의 주의 및 매도 의견.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', '하락', '상폐']</t>
+          <t>['하락', '공매도', '주의']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>232500</v>
+        <v>232000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.19%</t>
+          <t>'-7.39%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="G20" t="n">
-        <v>1650</v>
+        <v>1692</v>
       </c>
       <c r="H20" t="n">
         <v>46.3</v>
@@ -2266,7 +2266,7 @@
         <v>46.35</v>
       </c>
       <c r="O20" t="n">
-        <v>5143648136000</v>
+        <v>5621569760000</v>
       </c>
       <c r="P20" t="n">
         <v>374500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>현 정부 정책에 대한 부정적 평가와 함께 주가 하락 경험 공유. 외인 매도세 및 노조 관련 언급.</t>
+          <t>정부 정책 및 정치적 요인에 따른 주가 하락 우려. 기술 유출 관련 처벌 요구.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정부개입', '호남반도체', '외인매도']</t>
+          <t>['정치', '하락', '기술유출']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18890</v>
+        <v>18860</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.63%</t>
+          <t>'-7.78%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.39</v>
       </c>
       <c r="E21" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F21" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G21" t="n">
-        <v>491</v>
+        <v>520</v>
       </c>
       <c r="H21" t="n">
         <v>0.73</v>
@@ -2358,7 +2358,7 @@
         <v>0.34</v>
       </c>
       <c r="O21" t="n">
-        <v>100376259070</v>
+        <v>100571856130</v>
       </c>
       <c r="P21" t="n">
         <v>62100</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 계단식 하락 패턴으로 인한 투자 주의 필요.</t>
+          <t>신규 상장주에 대한 주가 조작 및 도박장 비유, 외부 조달 판매 의혹 제기. 계단식 하락 및 단주 거래에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 조작', '계단식 하락', '보호예수']</t>
+          <t>['주가 조작', '신규 상장주', '단주 거래']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12110</v>
+        <v>12150</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.63%</t>
+          <t>'-9.33%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.01</v>
       </c>
       <c r="E22" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F22" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G22" t="n">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>1.01</v>
       </c>
       <c r="O22" t="n">
-        <v>200043579885</v>
+        <v>200204640285</v>
       </c>
       <c r="P22" t="n">
         <v>19380</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주포의 움직임과 공매도에 대한 언급. 목표가 15000원 제시 및 호남 반도체 관련 기대.</t>
+          <t>주포 교체 및 공매도 영향으로 인한 주가 부진. 수주 발표 기대감.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주포', '공매도', '호남반도체']</t>
+          <t>['주포', '공매도', '수주']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,83 +2495,83 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1443000</v>
+        <v>6670</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.09%</t>
+          <t>'-9.99%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>171</v>
       </c>
       <c r="F23" t="n">
-        <v>579</v>
+        <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>1484</v>
+        <v>426</v>
       </c>
       <c r="H23" t="n">
-        <v>49.41</v>
+        <v>1.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1605000</v>
+        <v>7410</v>
       </c>
       <c r="K23" t="n">
-        <v>1538000</v>
+        <v>7330</v>
       </c>
       <c r="L23" t="n">
-        <v>1554000</v>
+        <v>8040</v>
       </c>
       <c r="M23" t="n">
-        <v>1425000</v>
+        <v>6580</v>
       </c>
       <c r="N23" t="n">
-        <v>49.52</v>
+        <v>1.99</v>
       </c>
       <c r="O23" t="n">
-        <v>7032658543000</v>
+        <v>72425354360</v>
       </c>
       <c r="P23" t="n">
-        <v>2987000</v>
+        <v>23500</v>
       </c>
       <c r="Q23" t="n">
-        <v>403000</v>
+        <v>2890</v>
       </c>
       <c r="R23" t="n">
-        <v>-1301000</v>
+        <v>-277000</v>
       </c>
       <c r="S23" t="n">
-        <v>114000</v>
+        <v>-218000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>현 정부 정책 및 이재명 관련 부정적 평가와 함께 주가 폭락 경험 공유. 외인 매도세 및 최태원 관련 언급.</t>
+          <t>성수 메가프로젝트 및 건설 기초소재 관련 언급. 매수 호가 대량 물량 및 매집 물량 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['이재명', '호남투자', '외인매도']</t>
+          <t>['건설기초소재', '매집', '호남반도체']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6640</v>
+        <v>1443000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.39%</t>
+          <t>'-10.09%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="E24" t="n">
-        <v>170</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>72</v>
+        <v>579</v>
       </c>
       <c r="G24" t="n">
-        <v>421</v>
+        <v>1612</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>49.41</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7410</v>
+        <v>1605000</v>
       </c>
       <c r="K24" t="n">
-        <v>7330</v>
+        <v>1538000</v>
       </c>
       <c r="L24" t="n">
-        <v>8040</v>
+        <v>1554000</v>
       </c>
       <c r="M24" t="n">
-        <v>6580</v>
+        <v>1425000</v>
       </c>
       <c r="N24" t="n">
-        <v>1.99</v>
+        <v>49.52</v>
       </c>
       <c r="O24" t="n">
-        <v>72145361100</v>
+        <v>7625523751000</v>
       </c>
       <c r="P24" t="n">
-        <v>23500</v>
+        <v>2987000</v>
       </c>
       <c r="Q24" t="n">
-        <v>2890</v>
+        <v>403000</v>
       </c>
       <c r="R24" t="n">
-        <v>-277000</v>
+        <v>-1301000</v>
       </c>
       <c r="S24" t="n">
-        <v>-218000</v>
+        <v>114000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>성수 메가프로젝트 및 건설 기초소재 관련 언급. 매수 호가 대량 물량 및 매집 물량 언급.</t>
+          <t>정치적 이슈 및 기업 경영 판단에 따른 급락 우려. 외인 매도세 지속.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['건설기초소재', '매집', '호남반도체']</t>
+          <t>['정치', '하락', '외인']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>000660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_15.xlsx
+++ b/data/trending_integrated_20261013_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F2" t="n">
         <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87909833670</v>
+        <v>87912344750</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>전남광주 경제자유구역 확대 추진 수혜 기대. 10년간 꿈쩍 않던 자리 돌파.</t>
+          <t>주가 급등세를 보이며 '왕', '대장' 등의 표현으로 강한 상승 기대감 형성. 경제자유구역 확대 수혜 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['경제자유구역', '수혜주', '상승']</t>
+          <t>['경제자유구역', '대규모 확대', '무차입 경영']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H3" t="n">
         <v>2.05</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>141841396310</v>
+        <v>141911756545</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>러시아 흑사병 테마 관련 신풍제약 비교 및 기대감 형성. 질병청 발표와 상반된 투자 심리.</t>
+          <t>러시아 흑사병 테마 관련주로 부각되며 급등 가능성 언급. 단, 질병청의 국내 발생 가능성 낮다는 뉴스 및 차트상 하락 추세도 관찰됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병', '치료제', '테마']</t>
+          <t>['흑사병 테마', '경영권 승계', '페스트']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="H4" t="n">
         <v>0.9399999999999999</v>
@@ -794,7 +794,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>37845152563</v>
+        <v>37847368278</v>
       </c>
       <c r="P4" t="n">
         <v>3280</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신한금융의 100% 지분 인수 확정 및 시너지 극대화 기대. 최소 2900원 공개매수 가격 제시.</t>
+          <t>신한금융의 100% 지분 인수 확정 소식을 바탕으로 급등 기대감 형성. 높은 분기 및 연매출과 시너지 효과 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신한금융', '인수', '호재']</t>
+          <t>['신한금융 인수', '지분 인수', '인수 확정']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -860,7 +860,7 @@
         <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H5" t="n">
         <v>0.88</v>
@@ -886,7 +886,7 @@
         <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>257807221015</v>
+        <v>258231027955</v>
       </c>
       <c r="P5" t="n">
         <v>19930</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 보안주 폭락 속에서 10% 이상 상승 기대. 디지털 자산 관련 내용 및 사명 변경 언급.</t>
+          <t>보안주로서의 상승 기대감과 함께 디지털 자산 관련 뉴스 언급. 미국 보안주 폭락에도 불구하고 상승 가능성 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '디지털자산', '급등']</t>
+          <t>['보안주', '디지털 자산', '단기 과열']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H6" t="n">
         <v>0.91</v>
@@ -978,7 +978,7 @@
         <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>104555958031</v>
+        <v>104570883671</v>
       </c>
       <c r="P6" t="n">
         <v>6660</v>
@@ -1038,7 +1038,7 @@
         <v>0.92</v>
       </c>
       <c r="E7" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F7" t="n">
         <v>144</v>
@@ -1070,7 +1070,7 @@
         <v>14.72</v>
       </c>
       <c r="O7" t="n">
-        <v>405253502495</v>
+        <v>405323134995</v>
       </c>
       <c r="P7" t="n">
         <v>14350</v>
@@ -1130,13 +1130,13 @@
         <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="H8" t="n">
         <v>27.69</v>
@@ -1162,7 +1162,7 @@
         <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>85616385335</v>
+        <v>85618661975</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1228,7 +1228,7 @@
         <v>145</v>
       </c>
       <c r="G9" t="n">
-        <v>1192</v>
+        <v>1206</v>
       </c>
       <c r="H9" t="n">
         <v>13.1</v>
@@ -1314,13 +1314,13 @@
         <v>-0.11</v>
       </c>
       <c r="E10" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F10" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G10" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H10" t="n">
         <v>22.1</v>
@@ -1346,7 +1346,7 @@
         <v>22.21</v>
       </c>
       <c r="O10" t="n">
-        <v>203893921250</v>
+        <v>203932320650</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1406,7 +1406,7 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F11" t="n">
         <v>28</v>
@@ -1438,7 +1438,7 @@
         <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>9578528574</v>
+        <v>9580361302</v>
       </c>
       <c r="P11" t="n">
         <v>2930</v>
@@ -1498,13 +1498,13 @@
         <v>-0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F12" t="n">
         <v>72</v>
       </c>
       <c r="G12" t="n">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="H12" t="n">
         <v>26.01</v>
@@ -1530,7 +1530,7 @@
         <v>26.37</v>
       </c>
       <c r="O12" t="n">
-        <v>31519347195</v>
+        <v>31522998675</v>
       </c>
       <c r="P12" t="n">
         <v>17950</v>
@@ -1622,7 +1622,7 @@
         <v>0.75</v>
       </c>
       <c r="O13" t="n">
-        <v>24596281095</v>
+        <v>24596587095</v>
       </c>
       <c r="P13" t="n">
         <v>11370</v>
@@ -1682,13 +1682,13 @@
         <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F14" t="n">
         <v>90</v>
       </c>
       <c r="G14" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H14" t="n">
         <v>12.27</v>
@@ -1714,7 +1714,7 @@
         <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>22985455505</v>
+        <v>22985606385</v>
       </c>
       <c r="P14" t="n">
         <v>8850</v>
@@ -1774,13 +1774,13 @@
         <v>0.16</v>
       </c>
       <c r="E15" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F15" t="n">
         <v>71</v>
       </c>
       <c r="G15" t="n">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="H15" t="n">
         <v>9.630000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>69591000000</v>
+        <v>69601000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H16" t="n">
         <v>0.46</v>
@@ -1898,7 +1898,7 @@
         <v>0.88</v>
       </c>
       <c r="O16" t="n">
-        <v>77570960980</v>
+        <v>77582438760</v>
       </c>
       <c r="P16" t="n">
         <v>30550</v>
@@ -1958,13 +1958,13 @@
         <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F17" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" t="n">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="H17" t="n">
         <v>3.43</v>
@@ -1990,7 +1990,7 @@
         <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>91020929930</v>
+        <v>91058631830</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 기록. 외인 매수세 유입에도 불구하고 주가 부진.</t>
+          <t>3분기 어닝 서프라이즈 달성 및 외인 대량 매수 소식에 기반한 상승 기대감. 미국 업체 대비 기술력 및 경쟁사 주가 하락 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '외인매수', '실적']</t>
+          <t>['어닝 서프라이즈', '외인 대량 매수', '광케이블']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>70</v>
       </c>
       <c r="G18" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H18" t="n">
         <v>75.20999999999999</v>
@@ -2082,7 +2082,7 @@
         <v>75.23</v>
       </c>
       <c r="O18" t="n">
-        <v>878915160450</v>
+        <v>879305592450</v>
       </c>
       <c r="P18" t="n">
         <v>243500</v>
@@ -2142,13 +2142,13 @@
         <v>0.09</v>
       </c>
       <c r="E19" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F19" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H19" t="n">
         <v>0.3</v>
@@ -2174,7 +2174,7 @@
         <v>0.21</v>
       </c>
       <c r="O19" t="n">
-        <v>70888761725</v>
+        <v>70900614735</v>
       </c>
       <c r="P19" t="n">
         <v>28700</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>고점 대비 큰 폭 하락 및 공매도 잔고 누적. 투자자들의 주의 및 매도 의견.</t>
+          <t>주가 급락 및 상장 폐지 가능성 언급. 공매도 잔량 및 주포의 움직임에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['하락', '공매도', '주의']</t>
+          <t>['공매도', '상장 폐지', '동전주']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="G20" t="n">
-        <v>1692</v>
+        <v>1670</v>
       </c>
       <c r="H20" t="n">
         <v>46.3</v>
@@ -2266,7 +2266,7 @@
         <v>46.35</v>
       </c>
       <c r="O20" t="n">
-        <v>5621569760000</v>
+        <v>5623250600000</v>
       </c>
       <c r="P20" t="n">
         <v>374500</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정부 정책 및 정치적 요인에 따른 주가 하락 우려. 기술 유출 관련 처벌 요구.</t>
+          <t>대통령 및 정치권에 대한 불만 표출과 함께 삼성전자 주가 하락 언급. 기술 유출 문제 해결 및 공무원 처벌 요구.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정치', '하락', '기술유출']</t>
+          <t>['기술 유출', '정치 테마', '성과급']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>0.39</v>
       </c>
       <c r="E21" t="n">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F21" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G21" t="n">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="H21" t="n">
         <v>0.73</v>
@@ -2358,7 +2358,7 @@
         <v>0.34</v>
       </c>
       <c r="O21" t="n">
-        <v>100571856130</v>
+        <v>100573025450</v>
       </c>
       <c r="P21" t="n">
         <v>62100</v>
@@ -2418,13 +2418,13 @@
         <v>-1.01</v>
       </c>
       <c r="E22" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F22" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G22" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>1.01</v>
       </c>
       <c r="O22" t="n">
-        <v>200204640285</v>
+        <v>200221091385</v>
       </c>
       <c r="P22" t="n">
         <v>19380</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주포 교체 및 공매도 영향으로 인한 주가 부진. 수주 발표 기대감.</t>
+          <t>주가 상승에 대한 기대감과 더불어 외인 매도 및 주포의 움직임에 대한 언급. 수주 발표 및 목표가 제시.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주포', '공매도', '수주']</t>
+          <t>['주포', '외인 매도', '수주 발표']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2510,13 +2510,13 @@
         <v>-0.19</v>
       </c>
       <c r="E23" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F23" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G23" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="H23" t="n">
         <v>1.8</v>
@@ -2542,7 +2542,7 @@
         <v>1.99</v>
       </c>
       <c r="O23" t="n">
-        <v>72425354360</v>
+        <v>72435786240</v>
       </c>
       <c r="P23" t="n">
         <v>23500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>성수 메가프로젝트 및 건설 기초소재 관련 언급. 매수 호가 대량 물량 및 매집 물량 언급.</t>
+          <t>대규모 건설 프로젝트 및 수도권 거점 공장 보유 기반으로 한 자산주로서의 상승 기대감. 하지만 주포의 움직임과 개인 매도에 대한 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['건설기초소재', '매집', '호남반도체']</t>
+          <t>['성수메가프로젝트', '건설기초소재', '자산주']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2605,10 +2605,10 @@
         <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="G24" t="n">
-        <v>1612</v>
+        <v>1698</v>
       </c>
       <c r="H24" t="n">
         <v>49.41</v>
@@ -2634,7 +2634,7 @@
         <v>49.52</v>
       </c>
       <c r="O24" t="n">
-        <v>7625523751000</v>
+        <v>7626561268000</v>
       </c>
       <c r="P24" t="n">
         <v>2987000</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 기업 경영 판단에 따른 급락 우려. 외인 매도세 지속.</t>
+          <t>정치적 이슈(호남 반도체 투자) 및 대주주 결정(솔리다임 상장 철회)에 대한 부정적 의견과 함께 주가 폭락 언급. 외인 매도세 지속.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['정치', '하락', '외인']</t>
+          <t>['호남 반도체', '쪼개기 상장', '정치 테마']</t>
         </is>
       </c>
       <c r="X24" t="n">
